--- a/Datas/NPCTaskScheduleData.xlsx
+++ b/Datas/NPCTaskScheduleData.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>bool</t>
+  </si>
+  <si>
+    <t>canBreak</t>
   </si>
 </sst>
 </file>
@@ -424,14 +427,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:E3"/>
+  <dimension ref="A2:F3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.875" customWidth="1"/>
     <col min="5" max="5" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -447,8 +450,11 @@
       <c r="E2" t="s">
         <v>8</v>
       </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -463,6 +469,9 @@
       </c>
       <c r="E3" t="s">
         <v>5</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/NPCTaskScheduleData.xlsx
+++ b/Datas/NPCTaskScheduleData.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -88,6 +88,21 @@
   </si>
   <si>
     <t>canBreak</t>
+  </si>
+  <si>
+    <t>睡眠</t>
+  </si>
+  <si>
+    <t>睡眠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>看守柜台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>家里闲逛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -427,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:F3"/>
+  <dimension ref="A2:F6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.875" customWidth="1"/>
@@ -474,6 +489,66 @@
         <v>9</v>
       </c>
     </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2000</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2001</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2002</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/NPCTaskScheduleData.xlsx
+++ b/Datas/NPCTaskScheduleData.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -103,6 +103,9 @@
   <si>
     <t>家里闲逛</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PauseWhenDisabled</t>
   </si>
 </sst>
 </file>
@@ -442,14 +445,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:F6"/>
+  <dimension ref="A2:G6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.875" customWidth="1"/>
     <col min="5" max="5" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -468,8 +471,11 @@
       <c r="F2" t="s">
         <v>8</v>
       </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -488,8 +494,11 @@
       <c r="F3" t="s">
         <v>9</v>
       </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2000</v>
       </c>
@@ -508,8 +517,11 @@
       <c r="F4" t="b">
         <v>0</v>
       </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2001</v>
       </c>
@@ -528,8 +540,11 @@
       <c r="F5" t="b">
         <v>0</v>
       </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2002</v>
       </c>
@@ -546,6 +561,9 @@
         <v>0</v>
       </c>
       <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Datas/NPCTaskScheduleData.xlsx
+++ b/Datas/NPCTaskScheduleData.xlsx
@@ -50,12 +50,38 @@
         </r>
       </text>
     </comment>
+    <comment ref="I3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>闲置=0,工作=1,睡眠=2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -106,6 +132,21 @@
   </si>
   <si>
     <t>PauseWhenDisabled</t>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>holdPos</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>behaviorState</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -445,14 +486,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:G6"/>
+  <dimension ref="A2:I6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.875" customWidth="1"/>
     <col min="5" max="5" width="15.25" customWidth="1"/>
+    <col min="7" max="7" width="12.875" customWidth="1"/>
+    <col min="9" max="9" width="12.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -474,8 +517,14 @@
       <c r="G2" t="s">
         <v>8</v>
       </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -497,8 +546,14 @@
       <c r="G3" t="s">
         <v>14</v>
       </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2000</v>
       </c>
@@ -520,8 +575,14 @@
       <c r="G4" t="b">
         <v>0</v>
       </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2001</v>
       </c>
@@ -543,8 +604,14 @@
       <c r="G5" t="b">
         <v>0</v>
       </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2002</v>
       </c>
@@ -564,6 +631,12 @@
         <v>0</v>
       </c>
       <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
     </row>

--- a/Datas/NPCTaskScheduleData.xlsx
+++ b/Datas/NPCTaskScheduleData.xlsx
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -117,9 +117,6 @@
   </si>
   <si>
     <t>睡眠</t>
-  </si>
-  <si>
-    <t>睡眠</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -147,6 +144,23 @@
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拜访</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>逛街</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>到玩家的商店买东西</t>
+  </si>
+  <si>
+    <t>参观玩家的家</t>
+  </si>
+  <si>
+    <t>逛商店</t>
   </si>
 </sst>
 </file>
@@ -486,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:I6"/>
+  <dimension ref="A2:I11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.875" customWidth="1"/>
@@ -518,10 +532,10 @@
         <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -544,13 +558,13 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" t="s">
         <v>16</v>
-      </c>
-      <c r="I3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -558,7 +572,7 @@
         <v>2000</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -587,13 +601,13 @@
         <v>2001</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -616,13 +630,13 @@
         <v>2002</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -631,12 +645,157 @@
         <v>0</v>
       </c>
       <c r="G6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2003</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2004</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>2005</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2006</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2007</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11">
         <v>0</v>
       </c>
     </row>

--- a/Datas/NPCTaskScheduleData.xlsx
+++ b/Datas/NPCTaskScheduleData.xlsx
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -161,6 +161,10 @@
   </si>
   <si>
     <t>逛商店</t>
+  </si>
+  <si>
+    <t>工作地点闲逛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -500,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:I11"/>
+  <dimension ref="A2:I12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.875" customWidth="1"/>
@@ -799,6 +803,35 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2008</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/NPCTaskScheduleData.xlsx
+++ b/Datas/NPCTaskScheduleData.xlsx
@@ -50,7 +50,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0" shapeId="0">
+    <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -98,9 +98,6 @@
   </si>
   <si>
     <t>behaviorName</t>
-  </si>
-  <si>
-    <t>loopBehavior</t>
   </si>
   <si>
     <t>string</t>
@@ -504,45 +501,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:I12"/>
+  <dimension ref="A2:H12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.875" customWidth="1"/>
-    <col min="5" max="5" width="15.25" customWidth="1"/>
-    <col min="7" max="7" width="12.875" customWidth="1"/>
-    <col min="9" max="9" width="12.25" customWidth="1"/>
+    <col min="6" max="6" width="12.875" customWidth="1"/>
+    <col min="8" max="8" width="12.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -556,33 +549,30 @@
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
       </c>
-      <c r="I3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2000</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -591,27 +581,24 @@
         <v>0</v>
       </c>
       <c r="G4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2001</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -620,215 +607,191 @@
         <v>0</v>
       </c>
       <c r="G5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2002</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2003</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2004</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>2005</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
       <c r="F9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>2006</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>2007</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2008</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <v>0</v>
       </c>
     </row>

--- a/Datas/NPCTaskScheduleData.xlsx
+++ b/Datas/NPCTaskScheduleData.xlsx
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -161,6 +161,13 @@
   </si>
   <si>
     <t>工作地点闲逛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxPauseTime</t>
+  </si>
+  <si>
+    <t>float</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -501,15 +508,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:H12"/>
+  <dimension ref="A2:I12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.875" customWidth="1"/>
     <col min="6" max="6" width="12.875" customWidth="1"/>
     <col min="8" max="8" width="12.25" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -534,8 +542,11 @@
       <c r="H2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -560,8 +571,11 @@
       <c r="H3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2000</v>
       </c>
@@ -586,8 +600,11 @@
       <c r="H4">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2001</v>
       </c>
@@ -612,8 +629,11 @@
       <c r="H5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2002</v>
       </c>
@@ -638,8 +658,11 @@
       <c r="H6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2003</v>
       </c>
@@ -664,8 +687,11 @@
       <c r="H7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2004</v>
       </c>
@@ -690,8 +716,11 @@
       <c r="H8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>2005</v>
       </c>
@@ -716,8 +745,11 @@
       <c r="H9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>2006</v>
       </c>
@@ -742,8 +774,11 @@
       <c r="H10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>2007</v>
       </c>
@@ -768,8 +803,11 @@
       <c r="H11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2008</v>
       </c>
@@ -793,6 +831,9 @@
       </c>
       <c r="H12">
         <v>0</v>
+      </c>
+      <c r="I12">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/NPCTaskScheduleData.xlsx
+++ b/Datas/NPCTaskScheduleData.xlsx
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="30">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -168,6 +168,26 @@
   </si>
   <si>
     <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>窝里闲逛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场地闲逛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吃东西</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动物睡眠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动物睡眠</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -226,8 +246,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -508,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:I12"/>
+  <dimension ref="A2:I16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.875" customWidth="1"/>
@@ -836,6 +857,122 @@
         <v>20</v>
       </c>
     </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2009</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2010</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2011</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2012</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>2</v>
+      </c>
+      <c r="I16">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/NPCTaskScheduleData.xlsx
+++ b/Datas/NPCTaskScheduleData.xlsx
@@ -533,6 +533,7 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.875" customWidth="1"/>
+    <col min="5" max="5" width="14.375" customWidth="1"/>
     <col min="6" max="6" width="12.875" customWidth="1"/>
     <col min="8" max="8" width="12.25" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
